--- a/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
+++ b/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,8 +670,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -680,37 +682,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +750,9 @@
       <c r="I4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -855,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -894,11 +898,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -928,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -958,7 +962,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -966,10 +970,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -978,39 +980,37 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1078,12 +1078,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1151,12 +1151,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1190,11 +1190,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1262,47 +1262,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1336,11 +1340,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1370,12 +1374,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1400,7 +1404,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1408,8 +1412,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>1</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1418,37 +1424,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1482,11 +1490,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1516,12 +1524,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1546,7 +1554,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1554,10 +1562,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1566,39 +1572,37 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1632,11 +1636,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1666,12 +1670,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1696,7 +1700,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1704,51 +1708,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1816,12 +1816,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1854,10 +1854,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1866,39 +1864,37 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1932,11 +1928,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1959,19 +1955,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1996,7 +1992,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2004,8 +2000,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2014,37 +2012,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2078,11 +2078,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2105,19 +2105,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2150,47 +2150,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2224,11 +2228,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2251,19 +2255,19 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2288,7 +2292,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2296,8 +2300,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>1</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2306,37 +2312,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2370,11 +2378,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2404,12 +2412,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2437,17 +2445,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2477,12 +2485,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2516,7 +2524,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2550,12 +2558,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2580,7 +2588,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2589,24 +2597,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2623,12 +2631,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2656,17 +2664,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2696,12 +2704,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2726,7 +2734,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2734,10 +2742,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2746,39 +2752,37 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2803,7 +2807,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2812,24 +2816,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2846,12 +2850,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2876,59 +2880,55 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2962,11 +2962,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2996,12 +2996,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3034,10 +3034,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3046,39 +3044,37 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3106,17 +3102,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3146,12 +3142,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3223,12 +3219,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3253,7 +3249,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3262,24 +3258,24 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3296,12 +3292,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3373,12 +3369,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3406,17 +3402,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3446,12 +3442,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3523,12 +3519,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3553,7 +3549,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3562,24 +3558,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>12</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3596,12 +3592,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3673,12 +3669,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3706,17 +3702,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3746,12 +3742,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3823,12 +3819,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3853,33 +3849,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▼ 90,2%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3896,12 +3892,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3973,12 +3969,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4012,16 +4008,16 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▲ 34,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4029,7 +4025,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4046,12 +4042,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4123,12 +4119,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4162,11 +4158,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4196,12 +4192,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4273,12 +4269,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4303,7 +4299,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4312,24 +4308,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
+        <v>5</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 90,2%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4346,12 +4342,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4423,12 +4419,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4453,33 +4449,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▲ 34,2%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4496,12 +4492,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4573,12 +4569,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4603,33 +4599,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 71,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 41,5%</t>
+        <v>38</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4646,12 +4642,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4676,7 +4672,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4684,8 +4680,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4694,37 +4692,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4749,33 +4749,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4830,47 +4830,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4895,33 +4899,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,8%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4938,12 +4942,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4968,7 +4972,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4976,47 +4980,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>1</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5041,25 +5049,25 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+          <t>R$ 71,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▼ 62,8%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -5067,7 +5075,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5084,12 +5092,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5123,7 +5131,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5145,7 +5153,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5157,12 +5165,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5187,33 +5195,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▲ 24,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5230,12 +5238,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5260,7 +5268,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5268,51 +5276,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5337,33 +5341,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,0%</t>
+          <t>▲ 18,8%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5380,12 +5384,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5410,7 +5414,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5418,51 +5422,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5487,33 +5487,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 331,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▲ 501,8%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▲ 97,3%</t>
+        <v>32</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 62,8%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5530,12 +5530,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5568,10 +5568,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5580,39 +5578,37 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5637,33 +5633,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 24,9%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+        <v>86</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
           <t>2,7%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5680,12 +5676,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5757,12 +5753,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5787,33 +5783,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 221,00</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+        <v>81</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5830,12 +5826,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5860,7 +5856,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5868,8 +5864,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5878,37 +5876,39 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5933,33 +5933,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 331,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 501,8%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,7%</t>
+          <t>▲ 97,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5976,12 +5976,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6014,47 +6014,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6079,33 +6083,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>37</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6122,78 +6126,520 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,7%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-033</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza sem pé -1740</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>4536532951</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="n">
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
+++ b/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,41 +680,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -748,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -898,11 +894,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,14 +928,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -962,7 +958,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -970,8 +966,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -980,39 +978,41 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1044,11 +1044,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1151,14 +1151,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1190,11 +1190,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1224,14 +1224,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1262,10 +1262,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1274,39 +1272,37 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1374,12 +1370,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1451,12 +1447,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1492,9 +1488,9 @@
       <c r="I14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1524,14 +1520,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1554,7 +1550,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1562,8 +1558,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1572,39 +1570,41 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1636,11 +1636,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1711,9 +1711,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1743,14 +1743,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1782,11 +1782,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1816,14 +1816,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1889,14 +1889,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1928,11 +1928,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1962,14 +1962,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2000,10 +2000,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2012,41 +2010,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2078,11 +2074,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2112,12 +2108,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2189,14 +2185,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2228,11 +2224,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2262,12 +2258,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2339,14 +2335,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2378,11 +2374,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2405,21 +2401,21 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2442,7 +2438,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2450,8 +2446,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2460,39 +2458,41 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2524,11 +2524,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2599,9 +2599,9 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2704,14 +2704,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2743,11 +2743,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2818,9 +2818,9 @@
       <c r="I32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2850,14 +2850,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2883,17 +2883,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2923,14 +2923,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2962,11 +2962,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2996,14 +2996,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3026,33 +3026,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3069,14 +3069,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3102,17 +3102,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3142,14 +3142,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3180,10 +3180,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3192,41 +3190,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3249,33 +3245,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3292,12 +3288,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3369,14 +3365,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3399,7 +3395,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3408,24 +3404,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3442,12 +3438,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3519,14 +3515,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3558,11 +3554,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▲ 1100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3592,12 +3588,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3669,14 +3665,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3708,11 +3704,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3742,12 +3738,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3819,14 +3815,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3852,17 +3848,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3892,12 +3888,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3969,14 +3965,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3999,33 +3995,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4042,12 +4038,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4119,14 +4115,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4149,33 +4145,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4192,12 +4188,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4269,14 +4265,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4299,33 +4295,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 90,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4342,12 +4338,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4419,14 +4415,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4454,20 +4450,20 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▲ 34,2%</t>
+          <t>▼ 90,2%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -4475,7 +4471,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4492,12 +4488,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4569,14 +4565,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4599,33 +4595,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>51</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,2%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4642,12 +4638,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4719,14 +4715,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4749,33 +4745,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4792,12 +4788,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4869,14 +4865,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4902,22 +4898,22 @@
           <t>R$ 142,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>38</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -4925,7 +4921,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4942,12 +4938,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5019,14 +5015,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5049,33 +5045,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 71,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5092,14 +5088,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5122,7 +5118,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5130,8 +5126,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5140,39 +5138,41 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5195,33 +5195,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 71,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5279,9 +5279,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5311,14 +5311,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5341,33 +5341,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 18,8%</t>
+        <v>41</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5384,14 +5384,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5423,11 +5423,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5457,14 +5457,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5490,22 +5490,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▼ 62,8%</t>
+          <t>▲ 18,8%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5530,12 +5530,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5603,14 +5603,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5633,33 +5633,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,9%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▼ 62,8%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5676,14 +5676,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5714,10 +5714,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5726,41 +5724,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5783,25 +5779,25 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
+          <t>R$ 276,00</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,2%</t>
+          <t>▲ 24,9%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,0%</t>
+        <v>86</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5809,7 +5805,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5826,12 +5822,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5903,14 +5899,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5933,33 +5929,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 331,00</t>
+          <t>R$ 221,00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>▲ 501,8%</t>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 97,3%</t>
+        <v>81</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5976,12 +5972,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6053,14 +6049,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6083,33 +6079,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 331,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 501,8%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▲ 97,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6126,12 +6122,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6203,14 +6199,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6236,22 +6232,22 @@
           <t>R$ 55,00</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+        <v>37</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
@@ -6259,7 +6255,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6276,14 +6272,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6306,7 +6302,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6314,8 +6310,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6324,39 +6322,41 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6379,33 +6379,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,7%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6422,12 +6422,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6463,9 +6463,9 @@
       <c r="I81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6495,14 +6495,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6530,20 +6530,20 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6568,14 +6568,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6607,11 +6607,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6638,8 +6638,154 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
+++ b/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,51 +816,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -894,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -928,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -958,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -966,51 +962,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1044,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1078,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1117,7 +1109,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1151,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1224,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1254,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1262,8 +1254,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1272,37 +1266,39 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1338,9 +1334,9 @@
       <c r="I12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1370,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1447,12 +1443,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1486,11 +1482,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1520,12 +1516,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1550,7 +1546,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1558,10 +1554,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1570,39 +1564,37 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1636,7 +1628,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1670,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1743,12 +1735,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1782,11 +1774,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1816,12 +1808,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1846,7 +1838,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1854,47 +1846,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1928,11 +1924,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1962,12 +1958,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1992,7 +1988,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2000,8 +1996,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>1</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2010,37 +2008,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2074,11 +2074,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2146,10 +2146,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2158,39 +2156,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2224,11 +2220,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2258,12 +2254,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2288,7 +2284,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2296,51 +2292,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2378,7 +2370,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2408,12 +2400,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2438,7 +2430,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2446,10 +2438,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2458,39 +2448,37 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2524,11 +2512,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2551,19 +2539,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2588,7 +2576,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2596,8 +2584,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2606,37 +2596,39 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2670,11 +2662,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2697,19 +2689,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2734,7 +2726,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2742,47 +2734,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2816,11 +2812,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2843,19 +2839,19 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2880,7 +2876,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2888,8 +2884,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>1</v>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2898,37 +2896,39 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2962,11 +2962,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2996,12 +2996,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3029,17 +3029,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3069,12 +3069,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3142,12 +3142,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3181,24 +3181,24 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3215,12 +3215,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3248,17 +3248,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3326,10 +3326,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3338,39 +3336,37 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3395,7 +3391,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3404,24 +3400,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3438,12 +3434,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3468,59 +3464,55 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3554,11 +3546,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3588,12 +3580,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3618,7 +3610,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3626,10 +3618,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3638,39 +3628,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3698,17 +3686,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3738,12 +3726,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3815,12 +3803,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3845,7 +3833,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3854,24 +3842,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3888,12 +3876,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3965,12 +3953,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3998,17 +3986,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4038,12 +4026,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4115,12 +4103,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4145,7 +4133,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4154,24 +4142,24 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>12</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4188,12 +4176,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4265,12 +4253,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4298,17 +4286,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4338,12 +4326,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4415,12 +4403,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4445,33 +4433,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 90,2%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4488,12 +4476,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4565,12 +4553,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4604,16 +4592,16 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
@@ -4621,7 +4609,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4638,12 +4626,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4715,12 +4703,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4754,11 +4742,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4788,12 +4776,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4865,12 +4853,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4895,7 +4883,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4904,24 +4892,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
+        <v>5</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,2%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4938,12 +4926,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5015,12 +5003,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5045,33 +5033,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▲ 34,2%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5088,12 +5076,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5165,12 +5153,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5195,33 +5183,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 71,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,5%</t>
+        <v>38</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5238,12 +5226,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5268,7 +5256,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5276,8 +5264,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5286,37 +5276,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5341,33 +5333,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5384,12 +5376,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5414,7 +5406,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5422,47 +5414,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5487,33 +5483,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,8%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5530,12 +5526,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5560,7 +5556,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5568,47 +5564,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>1</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5633,25 +5633,25 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+          <t>R$ 71,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,8%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5779,33 +5779,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5860,51 +5860,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5929,33 +5925,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,0%</t>
+          <t>▲ 18,8%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5972,12 +5968,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6002,7 +5998,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6010,51 +6006,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6079,33 +6071,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 331,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 501,8%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 97,3%</t>
+        <v>32</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,8%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6122,12 +6114,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6152,7 +6144,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6160,10 +6152,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6172,39 +6162,37 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6229,33 +6217,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,9%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+        <v>86</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
           <t>2,7%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6272,12 +6260,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6349,12 +6337,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6379,33 +6367,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 221,00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+        <v>81</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6422,12 +6410,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6452,7 +6440,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6460,8 +6448,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6470,37 +6460,39 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6525,33 +6517,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 331,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 501,8%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,7%</t>
+          <t>▲ 97,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6568,12 +6560,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6598,7 +6590,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6606,47 +6598,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6671,33 +6667,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>37</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6714,78 +6710,520 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,7%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-033</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza sem pé -1740</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>4536532951</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="n">
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
+++ b/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1254,51 +1254,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1332,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1366,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1396,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1404,51 +1400,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1482,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1516,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1555,7 +1547,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1589,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1662,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1692,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1700,8 +1692,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1710,37 +1704,39 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1776,9 +1772,9 @@
       <c r="I18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1808,12 +1804,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1885,12 +1881,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1924,11 +1920,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1958,12 +1954,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1988,7 +1984,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1996,10 +1992,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2008,39 +2002,37 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2074,7 +2066,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -2108,12 +2100,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2181,12 +2173,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2220,11 +2212,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2254,12 +2246,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2284,7 +2276,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2292,47 +2284,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2366,11 +2362,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2400,12 +2396,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2430,7 +2426,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2438,8 +2434,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>1</v>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2448,37 +2446,39 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2512,11 +2512,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2584,10 +2584,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2596,39 +2594,37 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2662,11 +2658,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2696,12 +2692,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2726,7 +2722,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2734,51 +2730,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2816,7 +2808,7 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2846,12 +2838,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2876,7 +2868,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2884,10 +2876,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2896,39 +2886,37 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2962,11 +2950,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2989,19 +2977,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3026,7 +3014,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3034,8 +3022,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3044,37 +3034,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3108,11 +3100,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3135,19 +3127,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3172,7 +3164,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3180,47 +3172,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3254,11 +3250,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3281,19 +3277,19 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3318,7 +3314,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3326,8 +3322,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>1</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3336,37 +3334,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3400,11 +3400,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3467,17 +3467,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3580,12 +3580,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3619,24 +3619,24 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3653,12 +3653,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3686,17 +3686,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3764,10 +3764,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3776,39 +3774,37 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3833,7 +3829,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3842,24 +3838,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3876,12 +3872,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3906,59 +3902,55 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3992,11 +3984,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4026,12 +4018,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4056,7 +4048,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4064,10 +4056,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4076,39 +4066,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4136,17 +4124,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4176,12 +4164,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4253,12 +4241,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4283,7 +4271,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4292,24 +4280,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4326,12 +4314,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4403,12 +4391,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4436,17 +4424,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4476,12 +4464,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4553,12 +4541,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4583,7 +4571,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4592,24 +4580,24 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>12</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4626,12 +4614,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4703,12 +4691,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4736,17 +4724,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4776,12 +4764,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4853,12 +4841,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4883,33 +4871,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 90,2%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4926,12 +4914,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5003,12 +4991,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5042,16 +5030,16 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -5059,7 +5047,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5076,12 +5064,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5153,12 +5141,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5192,11 +5180,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5226,12 +5214,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5303,12 +5291,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5333,7 +5321,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5342,24 +5330,24 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
+        <v>5</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,2%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5376,12 +5364,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5453,12 +5441,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5483,33 +5471,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▲ 34,2%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5526,12 +5514,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5603,12 +5591,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5633,33 +5621,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 71,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,5%</t>
+        <v>38</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5676,12 +5664,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5706,7 +5694,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5714,8 +5702,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5724,37 +5714,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5779,33 +5771,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5822,12 +5814,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5852,7 +5844,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5860,47 +5852,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5925,33 +5921,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,8%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5968,12 +5964,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5998,7 +5994,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6006,47 +6002,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>1</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6071,25 +6071,25 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+          <t>R$ 71,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,8%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6187,12 +6187,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6217,33 +6217,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6298,51 +6298,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6367,33 +6363,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,0%</t>
+          <t>▲ 18,8%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6410,12 +6406,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6440,7 +6436,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6448,51 +6444,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6517,33 +6509,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 331,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 501,8%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 97,3%</t>
+        <v>32</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,8%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6560,12 +6552,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6590,7 +6582,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6598,10 +6590,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6610,39 +6600,37 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6667,33 +6655,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,9%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+        <v>86</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
           <t>2,7%</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6710,12 +6698,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6787,12 +6775,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6817,33 +6805,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 221,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+        <v>81</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6860,12 +6848,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6890,7 +6878,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6898,8 +6886,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>0</v>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6908,37 +6898,39 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6963,33 +6955,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 331,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 501,8%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,7%</t>
+          <t>▲ 97,3%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7006,12 +6998,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7036,7 +7028,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7044,47 +7036,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7109,33 +7105,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>37</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7152,78 +7148,520 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,7%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-033</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza sem pé -1740</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>4536532951</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="n">
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
+++ b/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -594,20 +594,20 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1403,9 +1403,9 @@
       <c r="I13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1692,10 +1692,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1704,41 +1702,39 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1770,11 +1766,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1804,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1881,14 +1877,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1920,11 +1916,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1954,14 +1950,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1984,7 +1980,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1992,8 +1988,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2002,39 +2000,41 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2066,11 +2066,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2100,12 +2100,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2173,14 +2173,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2212,11 +2212,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2246,14 +2246,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2284,10 +2284,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2296,39 +2294,37 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2396,12 +2392,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2473,12 +2469,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2514,9 +2510,9 @@
       <c r="I28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2546,14 +2542,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2576,7 +2572,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2584,8 +2580,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2594,39 +2592,41 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2658,11 +2658,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2733,9 +2733,9 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2765,14 +2765,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2804,11 +2804,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2838,14 +2838,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2877,11 +2877,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2911,14 +2911,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2950,11 +2950,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2984,14 +2984,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3022,10 +3022,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3034,41 +3032,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3100,11 +3096,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3134,12 +3130,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3211,14 +3207,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3250,11 +3246,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3284,12 +3280,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3361,14 +3357,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3400,11 +3396,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3427,21 +3423,21 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3464,7 +3460,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3472,8 +3468,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3482,39 +3480,41 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3546,11 +3546,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3580,12 +3580,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3621,9 +3621,9 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3653,12 +3653,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3726,14 +3726,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3765,11 +3765,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3799,12 +3799,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3840,9 +3840,9 @@
       <c r="I46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3872,14 +3872,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3905,17 +3905,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3945,14 +3945,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3984,11 +3984,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4018,14 +4018,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4048,33 +4048,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4091,14 +4091,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4124,17 +4124,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4164,14 +4164,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4202,10 +4202,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4214,41 +4212,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4271,33 +4267,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4314,12 +4310,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4391,14 +4387,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4421,7 +4417,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4430,24 +4426,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4464,12 +4460,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4541,14 +4537,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4580,11 +4576,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 1100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4614,12 +4610,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4691,14 +4687,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4730,11 +4726,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4764,12 +4760,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4841,14 +4837,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4874,17 +4870,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4914,12 +4910,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4991,14 +4987,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5021,33 +5017,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5064,12 +5060,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5141,14 +5137,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5171,33 +5167,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5214,12 +5210,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5291,14 +5287,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5321,33 +5317,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5364,12 +5360,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5441,14 +5437,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5476,20 +5472,20 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,2%</t>
+          <t>▼ 90,2%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5497,7 +5493,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5514,12 +5510,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5591,14 +5587,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5621,33 +5617,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>51</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 34,2%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5664,12 +5660,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5741,14 +5737,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5771,33 +5767,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5814,12 +5810,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5891,14 +5887,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5924,22 +5920,22 @@
           <t>R$ 142,00</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>38</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -5947,7 +5943,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5964,12 +5960,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6041,14 +6037,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6071,33 +6067,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 71,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6114,14 +6110,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6144,7 +6140,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6152,8 +6148,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6162,39 +6160,41 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6217,33 +6217,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 71,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6301,9 +6301,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6333,14 +6333,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6363,33 +6363,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,8%</t>
+        <v>41</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6406,14 +6406,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6445,11 +6445,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6479,14 +6479,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6512,22 +6512,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,8%</t>
+          <t>▲ 18,8%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6552,12 +6552,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6625,14 +6625,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6655,33 +6655,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,9%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▼ 62,8%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6698,14 +6698,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6736,10 +6736,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6748,41 +6746,39 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6805,25 +6801,25 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
+          <t>R$ 276,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,2%</t>
+          <t>▲ 24,9%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,0%</t>
+        <v>86</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6831,7 +6827,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6848,12 +6844,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6925,14 +6921,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6955,33 +6951,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 331,00</t>
+          <t>R$ 221,00</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>▲ 501,8%</t>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 97,3%</t>
+        <v>81</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6998,12 +6994,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7075,14 +7071,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7105,33 +7101,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 331,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▲ 501,8%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▲ 97,3%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7148,12 +7144,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7225,14 +7221,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7258,22 +7254,22 @@
           <t>R$ 55,00</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+        <v>37</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
@@ -7281,7 +7277,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7298,14 +7294,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7328,7 +7324,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7336,8 +7332,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7346,39 +7344,41 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7401,33 +7401,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,7%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7485,9 +7485,9 @@
       <c r="I95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7517,14 +7517,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7552,20 +7552,20 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7590,14 +7590,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7629,11 +7629,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7660,8 +7660,154 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
+++ b/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,9 +671,9 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1549,9 +1549,9 @@
       <c r="I15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
       <c r="I18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>▲ 100,0%</t>
         </is>
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1838,51 +1838,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1918,9 +1914,9 @@
       <c r="I20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1950,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1980,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1988,10 +1984,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2000,39 +1994,37 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2066,11 +2058,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2100,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2130,7 +2122,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2138,8 +2130,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2148,37 +2142,39 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2212,11 +2208,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2246,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2276,7 +2272,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2284,8 +2280,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2294,37 +2292,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2358,11 +2358,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2430,10 +2430,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2442,39 +2440,37 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2508,11 +2504,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2542,12 +2538,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2572,7 +2568,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2580,10 +2576,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2592,39 +2586,37 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2660,9 +2652,9 @@
       <c r="I30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2692,12 +2684,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2722,7 +2714,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2730,8 +2722,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2740,37 +2734,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2804,11 +2800,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2838,12 +2834,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2868,7 +2864,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2876,47 +2872,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2950,11 +2950,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3057,12 +3057,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3098,9 +3098,9 @@
       <c r="I36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3168,51 +3168,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3246,11 +3242,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3280,12 +3276,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3310,7 +3306,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3318,10 +3314,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3330,39 +3324,37 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3396,11 +3388,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3430,12 +3422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3507,12 +3499,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3546,11 +3538,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3573,19 +3565,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3610,7 +3602,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3618,8 +3610,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3628,37 +3622,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3692,11 +3688,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3719,19 +3715,19 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3756,7 +3752,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3764,47 +3760,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3838,11 +3838,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3945,12 +3945,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3986,9 +3986,9 @@
       <c r="I48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4018,12 +4018,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4051,15 +4051,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -4091,12 +4091,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4164,12 +4164,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4212,15 +4212,15 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4270,17 +4270,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4340,59 +4340,55 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4417,7 +4413,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4426,24 +4422,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>2</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4460,12 +4456,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4490,7 +4486,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4498,10 +4494,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4510,39 +4504,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4570,17 +4562,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4610,12 +4602,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4687,12 +4679,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4717,7 +4709,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4726,24 +4718,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1100,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4760,12 +4752,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4837,12 +4829,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4876,11 +4868,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4910,12 +4902,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4987,12 +4979,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5020,17 +5012,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 1100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5060,12 +5052,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5137,12 +5129,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5167,7 +5159,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5176,24 +5168,24 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5210,12 +5202,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5287,12 +5279,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5320,17 +5312,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5360,12 +5352,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5437,12 +5429,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5472,20 +5464,20 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 90,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5493,7 +5485,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5510,12 +5502,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5587,12 +5579,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5617,33 +5609,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▲ 34,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5660,12 +5652,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5737,12 +5729,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5767,33 +5759,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,2%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5810,12 +5802,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5887,12 +5879,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5917,33 +5909,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
+        <v>51</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,2%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5960,12 +5952,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6037,12 +6029,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6067,33 +6059,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>38</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6110,12 +6102,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6187,12 +6179,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6217,33 +6209,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 71,00</t>
+          <t>R$ 142,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6260,12 +6252,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6290,7 +6282,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6298,8 +6290,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6308,37 +6302,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6363,33 +6359,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 142,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,9%</t>
+        <v>26</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6406,12 +6402,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6436,7 +6432,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6444,47 +6440,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6509,25 +6509,25 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 71,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,8%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6552,12 +6552,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6591,11 +6591,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -6625,12 +6625,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6655,33 +6655,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▼ 62,8%</t>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6737,11 +6737,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6771,12 +6771,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6801,33 +6801,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▲ 24,9%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+        <v>38</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,8%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6882,51 +6882,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6951,33 +6947,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,0%</t>
+          <t>▼ 62,8%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6994,12 +6990,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7024,7 +7020,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7032,10 +7028,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I89" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7044,39 +7038,37 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7101,33 +7093,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 331,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▲ 501,8%</t>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,9%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▲ 97,3%</t>
+        <v>86</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7144,12 +7136,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7221,12 +7213,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7251,33 +7243,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 221,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7294,12 +7286,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7371,12 +7363,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7401,33 +7393,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 331,00</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▲ 501,8%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▲ 97,3%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7444,12 +7436,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7474,7 +7466,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7482,8 +7474,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7492,37 +7486,39 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7547,7 +7543,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7556,24 +7552,24 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,7%</t>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7590,12 +7586,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7620,7 +7616,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7628,47 +7624,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7693,33 +7693,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>38</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7806,8 +7806,300 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,7%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
+++ b/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1103,17 +1103,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1255,24 +1255,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1483,15 +1483,15 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1619,47 +1619,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,7 +1688,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1695,22 +1699,22 @@
       <c r="I17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1731,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,7 +1761,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1765,47 +1769,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1839,7 +1847,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1873,12 +1881,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,7 +1911,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1911,47 +1919,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1985,11 +1997,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,7 +2061,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2057,47 +2069,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,7 +2138,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2130,51 +2146,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2199,7 +2211,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2207,47 +2219,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2272,7 +2288,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2280,51 +2296,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2358,11 +2370,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2392,12 +2404,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2431,11 +2443,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2465,12 +2477,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2498,17 +2510,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2538,12 +2550,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2577,11 +2589,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2611,12 +2623,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2641,33 +2653,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2684,12 +2696,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2714,7 +2726,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2722,51 +2734,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2791,7 +2799,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2800,24 +2808,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2834,12 +2842,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2864,7 +2872,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2872,51 +2880,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2950,11 +2954,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2984,12 +2988,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3023,7 +3027,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3057,12 +3061,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3096,11 +3100,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3130,12 +3134,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3203,12 +3207,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3242,11 +3246,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3276,12 +3280,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3315,11 +3319,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3349,12 +3353,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3388,11 +3392,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3422,12 +3426,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3452,7 +3456,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3460,51 +3464,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3538,11 +3538,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3572,12 +3572,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3610,51 +3610,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3688,11 +3684,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3722,12 +3718,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3752,7 +3748,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3760,10 +3756,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3772,39 +3766,37 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3838,11 +3830,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3865,19 +3857,19 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3902,7 +3894,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3910,8 +3902,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3920,37 +3914,39 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3984,11 +3980,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4011,19 +4007,19 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4048,7 +4044,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4056,47 +4052,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4130,11 +4130,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4157,19 +4157,19 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4230,19 +4230,19 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4276,11 +4276,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4303,19 +4303,19 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4343,17 +4343,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4376,19 +4376,19 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4449,19 +4449,19 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4494,8 +4494,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>1</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4504,37 +4506,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4562,17 +4566,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4595,19 +4599,19 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4679,12 +4683,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4709,7 +4713,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4718,24 +4722,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4745,19 +4749,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4782,7 +4786,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4790,10 +4794,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4802,39 +4804,37 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4868,11 +4868,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4895,19 +4895,19 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4940,51 +4940,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5018,11 +5014,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▲ 1100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5045,19 +5041,19 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5082,7 +5078,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5090,10 +5086,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5102,39 +5096,37 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5170,9 +5162,9 @@
       <c r="I64" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5195,19 +5187,19 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5279,12 +5271,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5312,17 +5304,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5345,19 +5337,19 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5429,12 +5421,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5459,7 +5451,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5468,24 +5460,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5495,19 +5487,19 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5579,12 +5571,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5612,17 +5604,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5652,12 +5644,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5682,7 +5674,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5690,10 +5682,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5702,39 +5692,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5759,33 +5747,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,2%</t>
-        </is>
-      </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5802,12 +5790,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5832,7 +5820,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5840,51 +5828,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5909,7 +5893,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5918,24 +5902,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,2%</t>
+        <v>3</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5952,12 +5936,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5982,7 +5966,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5990,10 +5974,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6002,39 +5984,37 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6062,17 +6042,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6102,12 +6082,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6132,59 +6112,55 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6209,33 +6185,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
-        </is>
-      </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6252,12 +6228,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6282,7 +6258,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6290,10 +6266,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6302,39 +6276,37 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6359,33 +6331,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6402,12 +6374,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6479,12 +6451,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6509,7 +6481,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 71,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6518,16 +6490,16 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,5%</t>
+        <v>10</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6535,7 +6507,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6552,12 +6524,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6582,7 +6554,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6590,8 +6562,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6600,37 +6574,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6658,17 +6634,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,9%</t>
+        <v>9</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6698,12 +6674,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6728,7 +6704,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6736,47 +6712,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6801,33 +6781,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,8%</t>
+          <t>▲ 1100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6844,12 +6824,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6874,7 +6854,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6882,47 +6862,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>1</v>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6947,33 +6931,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,8%</t>
+        <v>1</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6990,12 +6974,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7020,7 +7004,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7028,8 +7012,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>1</v>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7038,37 +7024,39 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7093,33 +7081,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+        <v>1</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7136,12 +7124,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7213,12 +7201,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7243,33 +7231,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7286,12 +7274,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7363,12 +7351,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7393,33 +7381,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 331,00</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 501,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 97,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7436,12 +7424,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7513,12 +7501,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7543,7 +7531,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7552,16 +7540,16 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▼ 90,2%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
@@ -7569,7 +7557,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7586,12 +7574,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7663,12 +7651,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7693,25 +7681,25 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+        <v>51</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,2%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
@@ -7719,7 +7707,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7736,12 +7724,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7766,7 +7754,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7774,8 +7762,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7784,37 +7774,39 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7839,33 +7831,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I100" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,7%</t>
-        </is>
-      </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7882,12 +7874,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7912,7 +7904,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7920,47 +7912,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7985,33 +7981,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
+          <t>R$ 142,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>38</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8028,78 +8024,1854 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 71,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,5%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,8%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,8%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,9%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 221,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,0%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 331,00</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 501,8%</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 97,3%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,7%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-033</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza sem pé -1740</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>4536532951</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="n">
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="n">
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
+++ b/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,8 +597,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>9</v>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -607,37 +609,39 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +675,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -743,8 +747,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -753,37 +759,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,17 +819,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -889,8 +897,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -899,37 +909,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +966,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1070,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1112,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1155,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1176,9 +1188,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
@@ -1216,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1258,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1255,24 +1267,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 700,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1301,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1331,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1374,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,11 +1413,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1447,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,7 +1477,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1476,22 +1488,22 @@
       <c r="I14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1520,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1541,17 +1553,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1593,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,7 +1623,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1619,51 +1631,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1688,7 +1696,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1697,24 +1705,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1731,12 +1739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1761,7 +1769,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1769,51 +1777,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1849,9 +1853,9 @@
       <c r="I19" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1881,12 +1885,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1911,7 +1915,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1919,10 +1923,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1931,39 +1933,37 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1997,11 +1997,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2061,59 +2061,55 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2149,9 +2145,9 @@
       <c r="I23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2181,12 +2177,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2211,7 +2207,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2219,51 +2215,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2297,11 +2289,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2331,12 +2323,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2370,11 +2362,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2404,12 +2396,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2443,11 +2435,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2477,12 +2469,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2510,17 +2502,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2550,12 +2542,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2589,11 +2581,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2623,12 +2615,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2653,33 +2645,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2696,12 +2688,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2739,7 +2731,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2769,12 +2761,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2799,7 +2791,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2808,24 +2800,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2842,12 +2834,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2881,11 +2873,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2915,12 +2907,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2954,11 +2946,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2988,12 +2980,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3027,7 +3019,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3061,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3100,11 +3092,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3134,12 +3126,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3207,12 +3199,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3246,11 +3238,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3280,12 +3272,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3319,7 +3311,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3353,12 +3345,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3386,17 +3378,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3426,12 +3418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3465,11 +3457,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3499,12 +3491,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3529,7 +3521,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3538,24 +3530,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3572,12 +3564,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3611,11 +3603,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3645,12 +3637,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3684,11 +3676,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3718,12 +3710,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3759,9 +3751,9 @@
       <c r="I45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3791,12 +3783,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3830,11 +3822,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3864,12 +3856,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3894,7 +3886,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3902,51 +3894,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I47" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3980,11 +3968,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4014,12 +4002,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4044,7 +4032,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4052,51 +4040,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4130,11 +4114,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4164,12 +4148,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4197,17 +4181,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4237,12 +4221,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4276,11 +4260,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4310,12 +4294,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4340,7 +4324,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4349,24 +4333,24 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4383,12 +4367,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4416,17 +4400,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4456,12 +4440,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4486,7 +4470,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4494,51 +4478,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4563,7 +4543,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4572,24 +4552,24 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4606,12 +4586,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4636,59 +4616,55 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4713,7 +4689,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4721,47 +4697,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4786,7 +4766,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4795,24 +4775,24 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4829,12 +4809,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4859,7 +4839,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4867,47 +4847,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4941,11 +4925,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4975,12 +4959,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5005,7 +4989,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5013,47 +4997,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5087,11 +5075,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5121,12 +5109,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5151,7 +5139,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5159,47 +5147,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5224,7 +5216,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5232,51 +5224,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I65" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5301,7 +5289,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5309,47 +5297,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5374,7 +5366,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5382,51 +5374,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5460,11 +5448,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5494,12 +5482,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5524,7 +5512,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5532,51 +5520,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5604,17 +5588,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5637,19 +5621,19 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5683,11 +5667,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5710,19 +5694,19 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5747,33 +5731,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5783,19 +5767,19 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5829,11 +5813,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5856,19 +5840,19 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5893,7 +5877,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5902,24 +5886,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5929,19 +5913,19 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5975,11 +5959,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6002,19 +5986,19 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6048,11 +6032,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6075,19 +6059,19 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6115,17 +6099,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6148,19 +6132,19 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6194,11 +6178,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6221,19 +6205,19 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6258,7 +6242,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6267,24 +6251,24 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6294,19 +6278,19 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6334,17 +6318,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6367,19 +6351,19 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6404,7 +6388,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6412,51 +6396,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6481,7 +6461,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6490,24 +6470,24 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6517,19 +6497,19 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6554,7 +6534,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6562,51 +6542,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6640,11 +6616,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6667,19 +6643,19 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6704,7 +6680,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6712,51 +6688,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I85" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6790,11 +6762,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6817,19 +6789,19 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6854,7 +6826,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6862,10 +6834,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6874,39 +6844,37 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6940,11 +6908,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6967,19 +6935,19 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7051,12 +7019,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7084,17 +7052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7117,19 +7085,19 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7201,12 +7169,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7231,7 +7199,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7240,24 +7208,24 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7267,19 +7235,19 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7304,7 +7272,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7312,10 +7280,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7324,39 +7290,37 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7384,17 +7348,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7417,19 +7381,19 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7454,7 +7418,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7462,10 +7426,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7474,39 +7436,37 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7531,33 +7491,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,2%</t>
-        </is>
-      </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7567,19 +7527,19 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7651,12 +7611,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7681,7 +7641,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7690,24 +7650,24 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7717,19 +7677,19 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7801,12 +7761,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7834,17 +7794,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7867,19 +7827,19 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7904,7 +7864,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7912,10 +7872,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -7924,39 +7882,37 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7981,33 +7937,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
+        <v>1</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8017,19 +7973,19 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8054,7 +8010,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8062,51 +8018,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8131,33 +8083,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8167,19 +8119,19 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8204,7 +8156,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8212,10 +8164,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I105" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8224,39 +8174,37 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8281,7 +8229,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 71,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8290,24 +8238,24 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8317,19 +8265,19 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8354,7 +8302,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8362,8 +8310,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="2" t="n">
-        <v>0</v>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -8372,37 +8322,39 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8430,17 +8382,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8463,19 +8415,19 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8500,7 +8452,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8508,47 +8460,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8573,33 +8529,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,8%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8609,19 +8565,19 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8646,7 +8602,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8654,47 +8610,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>1</v>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8719,33 +8679,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,8%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8762,12 +8722,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8801,7 +8761,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -8835,12 +8795,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8865,33 +8825,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+        <v>3</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8908,12 +8868,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8938,7 +8898,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -8946,51 +8906,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9015,33 +8971,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9058,12 +9014,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9088,7 +9044,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9096,10 +9052,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
@@ -9108,39 +9062,37 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9165,33 +9117,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 331,00</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 501,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▲ 97,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9208,12 +9160,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9238,59 +9190,55 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9315,33 +9263,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I120" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
-        </is>
-      </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9358,12 +9306,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9388,7 +9336,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9396,10 +9344,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9408,39 +9354,37 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9465,33 +9409,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9508,12 +9452,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9538,7 +9482,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9546,8 +9490,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="n">
-        <v>0</v>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9556,37 +9502,39 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9611,33 +9559,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,7%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9654,12 +9602,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9684,7 +9632,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9692,47 +9640,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9757,7 +9709,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9766,24 +9718,24 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9800,78 +9752,3204 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1100,0%</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,2%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,2%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 46,2%</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 71,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,5%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,8%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,8%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,9%</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 221,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,0%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 331,00</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 501,8%</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 97,3%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,7%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-033</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza sem pé -1740</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>4536532951</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="n">
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
+++ b/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 78,90</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">

--- a/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
+++ b/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,10 +597,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -609,41 +607,39 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -675,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -709,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,14 +782,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -819,17 +815,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -859,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,14 +932,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -966,33 +962,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1009,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1039,7 +1035,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1047,8 +1043,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1057,39 +1055,41 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1117,20 +1117,20 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1155,14 +1155,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1188,17 +1188,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1228,14 +1228,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1267,24 +1267,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 700,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1301,14 +1301,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1331,33 +1331,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1374,14 +1374,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1413,11 +1413,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1447,14 +1447,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1486,24 +1486,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1520,14 +1520,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1593,14 +1593,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1632,11 +1632,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1666,14 +1666,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1707,9 +1707,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1739,12 +1739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1812,14 +1812,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1851,11 +1851,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1958,14 +1958,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1997,11 +1997,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2031,14 +2031,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2064,17 +2064,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2104,14 +2104,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2143,11 +2143,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2177,14 +2177,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2207,33 +2207,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2250,14 +2250,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2323,14 +2323,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2362,24 +2362,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2396,14 +2396,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2437,9 +2437,9 @@
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2469,14 +2469,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2508,11 +2508,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2542,14 +2542,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2581,11 +2581,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2615,14 +2615,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2688,14 +2688,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2761,12 +2761,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2834,14 +2834,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2873,11 +2873,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2980,14 +2980,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3053,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3126,14 +3126,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3167,9 +3167,9 @@
       <c r="I37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3199,14 +3199,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3240,9 +3240,9 @@
       <c r="I38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3272,14 +3272,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3311,11 +3311,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3345,14 +3345,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3378,17 +3378,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3459,9 +3459,9 @@
       <c r="I41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3491,14 +3491,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3521,33 +3521,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 77,8%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3564,14 +3564,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3603,11 +3603,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3637,14 +3637,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3676,24 +3676,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3710,14 +3710,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3749,11 +3749,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3783,14 +3783,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3856,14 +3856,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3895,11 +3895,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4002,14 +4002,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4041,11 +4041,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4148,14 +4148,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4181,17 +4181,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4221,14 +4221,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4262,9 +4262,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4294,14 +4294,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4324,33 +4324,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4367,14 +4367,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4400,17 +4400,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4440,14 +4440,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4479,24 +4479,24 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4513,14 +4513,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4543,33 +4543,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4586,14 +4586,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4619,17 +4619,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4659,14 +4659,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4697,10 +4697,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I58" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4709,41 +4707,39 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4766,16 +4762,16 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4784,15 +4780,15 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4809,12 +4805,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4886,14 +4882,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4916,7 +4912,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4925,24 +4921,24 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4959,12 +4955,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5036,14 +5032,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5075,11 +5071,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5109,12 +5105,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5186,14 +5182,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5225,11 +5221,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5259,12 +5255,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5336,14 +5332,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5375,11 +5371,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5409,14 +5405,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5439,7 +5435,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5447,8 +5443,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5457,39 +5455,41 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5521,11 +5521,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5555,14 +5555,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5588,17 +5588,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5628,14 +5628,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5667,11 +5667,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5701,14 +5701,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5731,33 +5731,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5815,9 +5815,9 @@
       <c r="I73" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5847,14 +5847,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5882,20 +5882,20 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5920,14 +5920,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5959,11 +5959,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5993,14 +5993,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6032,24 +6032,24 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6066,14 +6066,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6105,11 +6105,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6139,14 +6139,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6178,11 +6178,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6212,14 +6212,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6251,11 +6251,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6285,14 +6285,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6324,11 +6324,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6358,14 +6358,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6397,11 +6397,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6431,14 +6431,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6470,11 +6470,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6577,14 +6577,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6616,11 +6616,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6650,12 +6650,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6691,9 +6691,9 @@
       <c r="I85" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6723,14 +6723,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6762,11 +6762,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6796,14 +6796,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6835,11 +6835,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6869,14 +6869,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6908,11 +6908,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6942,14 +6942,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6980,10 +6980,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I89" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -6992,41 +6990,39 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7058,11 +7054,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7092,12 +7088,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7169,14 +7165,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7208,11 +7204,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7242,14 +7238,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7272,7 +7268,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7280,8 +7276,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7290,39 +7288,41 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7354,11 +7354,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7461,14 +7461,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7500,11 +7500,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7534,14 +7534,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7572,10 +7572,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7584,39 +7582,37 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7684,12 +7680,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7761,12 +7757,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7802,9 +7798,9 @@
       <c r="I100" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7834,14 +7830,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7864,7 +7860,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7872,8 +7868,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -7882,39 +7880,41 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7946,11 +7946,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7980,14 +7980,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8021,9 +8021,9 @@
       <c r="I103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8053,14 +8053,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8092,11 +8092,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8126,14 +8126,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8165,11 +8165,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8199,14 +8199,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8238,11 +8238,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8272,14 +8272,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8310,10 +8310,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I107" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -8322,41 +8320,39 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8388,11 +8384,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8422,12 +8418,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8499,14 +8495,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8538,11 +8534,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8572,12 +8568,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8649,14 +8645,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8688,11 +8684,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8715,21 +8711,21 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8752,7 +8748,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -8760,8 +8756,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I113" s="2" t="n">
-        <v>0</v>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -8770,39 +8768,41 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8834,11 +8834,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8868,14 +8868,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8909,9 +8909,9 @@
       <c r="I115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8941,12 +8941,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9014,14 +9014,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9053,11 +9053,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9128,9 +9128,9 @@
       <c r="I118" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9160,14 +9160,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9193,17 +9193,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9233,14 +9233,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9272,11 +9272,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9306,14 +9306,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9336,33 +9336,33 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9379,14 +9379,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9412,17 +9412,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9452,14 +9452,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9490,10 +9490,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9502,41 +9500,39 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9559,33 +9555,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>2</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9602,12 +9598,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9679,14 +9675,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9709,7 +9705,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9718,24 +9714,24 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9752,12 +9748,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9829,14 +9825,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9868,11 +9864,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9902,12 +9898,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9979,14 +9975,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10018,11 +10014,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1100,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10052,12 +10048,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10129,14 +10125,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10162,17 +10158,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10202,12 +10198,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10279,14 +10275,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10309,33 +10305,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10352,12 +10348,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10429,14 +10425,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10459,33 +10455,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10502,12 +10498,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10579,14 +10575,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10609,33 +10605,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>▼ 90,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10652,12 +10648,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10729,14 +10725,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10764,20 +10760,20 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>▲ 34,2%</t>
+        <v>5</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,2%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
@@ -10785,7 +10781,7 @@
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10802,12 +10798,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10879,14 +10875,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10909,33 +10905,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>51</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,2%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -10952,12 +10948,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11029,14 +11025,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11059,33 +11055,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11102,12 +11098,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11179,14 +11175,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11212,22 +11208,22 @@
           <t>R$ 142,00</t>
         </is>
       </c>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
@@ -11235,7 +11231,7 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11252,12 +11248,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11329,14 +11325,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11359,33 +11355,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 71,00</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,5%</t>
+        <v>26</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11402,14 +11398,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11432,7 +11428,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11440,8 +11436,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="n">
-        <v>0</v>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11450,39 +11448,41 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11505,33 +11505,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 71,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,9%</t>
+        <v>24</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11548,14 +11548,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11589,9 +11589,9 @@
       <c r="I151" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -11621,14 +11621,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11651,33 +11651,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,8%</t>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11694,14 +11694,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11733,11 +11733,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11767,14 +11767,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11800,22 +11800,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,8%</t>
+        <v>38</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,8%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11913,14 +11913,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11943,33 +11943,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,9%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 6,2%</t>
+        <v>32</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,8%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11986,14 +11986,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12024,10 +12024,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I157" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
@@ -12036,41 +12034,39 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12093,25 +12089,25 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
-        </is>
-      </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24,9%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,0%</t>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
@@ -12119,7 +12115,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12136,12 +12132,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12213,14 +12209,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12243,33 +12239,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 331,00</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 501,8%</t>
+          <t>R$ 221,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▲ 97,3%</t>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12286,12 +12282,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12363,14 +12359,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12393,33 +12389,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 331,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 501,8%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+        <v>73</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 97,3%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12436,12 +12432,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12513,14 +12509,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12546,22 +12542,22 @@
           <t>R$ 55,00</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
@@ -12569,7 +12565,7 @@
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12586,14 +12582,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12616,7 +12612,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12624,8 +12620,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" s="2" t="n">
-        <v>0</v>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
@@ -12634,39 +12632,41 @@
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12689,33 +12689,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,7%</t>
+        <v>38</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12732,14 +12732,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12773,9 +12773,9 @@
       <c r="I167" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12805,14 +12805,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12840,20 +12840,20 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,7%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12878,78 +12878,224 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-033</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza sem pé -1740</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>4536532951</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="n">
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
+++ b/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -743,10 +743,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -755,41 +753,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -821,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -855,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -932,14 +928,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -965,17 +961,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1005,12 +1001,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1082,14 +1078,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1112,33 +1108,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1155,14 +1151,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1185,7 +1181,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1193,8 +1189,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1203,39 +1201,41 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1263,20 +1263,20 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1301,14 +1301,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1334,17 +1334,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1374,14 +1374,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1413,24 +1413,24 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 700,0%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1447,14 +1447,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1477,33 +1477,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1520,14 +1520,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1593,14 +1593,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1632,24 +1632,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1666,14 +1666,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1739,14 +1739,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1778,11 +1778,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1812,14 +1812,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1853,9 +1853,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1958,14 +1958,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1997,11 +1997,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2104,14 +2104,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2143,11 +2143,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2177,14 +2177,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2210,17 +2210,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2250,14 +2250,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2289,11 +2289,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2323,14 +2323,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2353,33 +2353,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2396,14 +2396,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2469,14 +2469,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2508,24 +2508,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2542,14 +2542,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2583,9 +2583,9 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2615,14 +2615,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2654,11 +2654,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2688,14 +2688,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2761,14 +2761,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2834,14 +2834,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2873,11 +2873,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2980,14 +2980,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3019,11 +3019,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3126,14 +3126,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3199,12 +3199,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3272,14 +3272,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3313,9 +3313,9 @@
       <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3345,14 +3345,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3386,9 +3386,9 @@
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3418,14 +3418,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3457,11 +3457,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3491,14 +3491,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3524,17 +3524,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3605,9 +3605,9 @@
       <c r="I43" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3637,14 +3637,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3667,33 +3667,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 77,8%</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3710,14 +3710,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3749,11 +3749,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3783,14 +3783,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3822,24 +3822,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3856,14 +3856,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3895,11 +3895,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3929,14 +3929,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4002,14 +4002,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4041,11 +4041,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4148,14 +4148,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4187,11 +4187,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4294,14 +4294,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4327,17 +4327,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4367,14 +4367,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4408,9 +4408,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4440,14 +4440,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4470,33 +4470,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4513,14 +4513,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4546,17 +4546,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4586,14 +4586,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4625,24 +4625,24 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4659,14 +4659,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4689,33 +4689,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4732,14 +4732,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4765,17 +4765,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4805,14 +4805,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4843,10 +4843,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4855,41 +4853,39 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4912,33 +4908,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4955,12 +4951,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5032,14 +5028,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5062,7 +5058,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5071,24 +5067,24 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5105,12 +5101,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5182,14 +5178,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5221,11 +5217,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5255,12 +5251,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5332,14 +5328,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5371,11 +5367,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5405,12 +5401,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5482,14 +5478,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5521,11 +5517,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5555,14 +5551,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5585,7 +5581,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5593,8 +5589,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5603,39 +5601,41 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5667,11 +5667,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5701,14 +5701,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5734,17 +5734,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5774,14 +5774,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5813,11 +5813,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5847,14 +5847,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5877,33 +5877,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5961,9 +5961,9 @@
       <c r="I75" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5993,14 +5993,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6028,20 +6028,20 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6066,14 +6066,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6105,11 +6105,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6139,14 +6139,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6178,24 +6178,24 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>1</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6212,14 +6212,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6251,11 +6251,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6285,14 +6285,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6324,11 +6324,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6358,14 +6358,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6397,11 +6397,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6431,14 +6431,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6470,11 +6470,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6504,14 +6504,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6543,11 +6543,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6577,14 +6577,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6616,11 +6616,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6650,12 +6650,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6723,14 +6723,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6762,11 +6762,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6837,9 +6837,9 @@
       <c r="I87" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6869,14 +6869,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6908,11 +6908,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6942,14 +6942,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6981,11 +6981,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7015,14 +7015,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7054,11 +7054,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7088,14 +7088,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7126,10 +7126,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7138,41 +7136,39 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7204,11 +7200,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7238,12 +7234,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7315,14 +7311,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7354,11 +7350,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7388,14 +7384,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7418,7 +7414,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7426,8 +7422,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7436,39 +7434,41 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7500,11 +7500,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7607,14 +7607,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7646,11 +7646,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7680,14 +7680,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7718,10 +7718,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7730,39 +7728,37 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7830,12 +7826,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7907,12 +7903,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7948,9 +7944,9 @@
       <c r="I102" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7980,14 +7976,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8010,7 +8006,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8018,8 +8014,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="n">
-        <v>0</v>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -8028,39 +8026,41 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8092,11 +8092,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8126,14 +8126,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8167,9 +8167,9 @@
       <c r="I105" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8199,14 +8199,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8238,11 +8238,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8272,14 +8272,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8311,11 +8311,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8345,14 +8345,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8384,11 +8384,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8418,14 +8418,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8456,10 +8456,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I109" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -8468,41 +8466,39 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8534,11 +8530,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8568,12 +8564,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8645,14 +8641,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8684,11 +8680,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8718,12 +8714,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8795,14 +8791,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8834,11 +8830,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8861,21 +8857,21 @@
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8898,7 +8894,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -8906,8 +8902,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="n">
-        <v>0</v>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -8916,39 +8914,41 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8980,11 +8980,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9014,14 +9014,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9055,9 +9055,9 @@
       <c r="I117" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9160,14 +9160,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9199,11 +9199,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9274,9 +9274,9 @@
       <c r="I120" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9306,14 +9306,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9339,17 +9339,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9379,14 +9379,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9418,11 +9418,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9452,14 +9452,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9482,33 +9482,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9525,14 +9525,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9558,17 +9558,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9598,14 +9598,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9628,7 +9628,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9636,10 +9636,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -9648,41 +9646,39 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9705,33 +9701,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9748,12 +9744,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9825,14 +9821,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9855,7 +9851,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -9864,24 +9860,24 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9898,12 +9894,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9975,14 +9971,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10014,11 +10010,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>▲ 1100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10048,12 +10044,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10125,14 +10121,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10164,11 +10160,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1100,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10198,12 +10194,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10275,14 +10271,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10308,17 +10304,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10348,12 +10344,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10425,14 +10421,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10455,33 +10451,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10498,12 +10494,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10575,14 +10571,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10605,33 +10601,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10648,12 +10644,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10725,14 +10721,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10755,33 +10751,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10798,12 +10794,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10875,14 +10871,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10910,20 +10906,20 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,2%</t>
+          <t>▼ 90,2%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
@@ -10931,7 +10927,7 @@
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -10948,12 +10944,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11025,14 +11021,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11055,33 +11051,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>51</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▲ 34,2%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11098,12 +11094,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11175,14 +11171,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11205,33 +11201,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11248,12 +11244,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11325,14 +11321,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11358,22 +11354,22 @@
           <t>R$ 142,00</t>
         </is>
       </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>38</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
@@ -11381,7 +11377,7 @@
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11398,12 +11394,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11475,14 +11471,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11505,33 +11501,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 71,00</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11548,14 +11544,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11578,7 +11574,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11586,8 +11582,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="2" t="n">
-        <v>0</v>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11596,39 +11594,41 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11651,33 +11651,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 71,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11694,14 +11694,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11735,9 +11735,9 @@
       <c r="I153" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -11767,14 +11767,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11797,33 +11797,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,8%</t>
+        <v>41</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11840,14 +11840,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11879,11 +11879,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11913,14 +11913,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11946,22 +11946,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,8%</t>
+          <t>▲ 18,8%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12059,14 +12059,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12089,33 +12089,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>▲ 24,9%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▼ 62,8%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12132,14 +12132,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12170,10 +12170,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I159" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12182,41 +12180,39 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12239,25 +12235,25 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
+          <t>R$ 276,00</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,2%</t>
+          <t>▲ 24,9%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,0%</t>
+        <v>86</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
@@ -12265,7 +12261,7 @@
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12282,12 +12278,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12359,14 +12355,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12389,33 +12385,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 331,00</t>
+          <t>R$ 221,00</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>▲ 501,8%</t>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 97,3%</t>
+        <v>81</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12432,12 +12428,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12509,14 +12505,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12539,33 +12535,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 331,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▲ 501,8%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▲ 97,3%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12582,12 +12578,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12659,14 +12655,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12692,22 +12688,22 @@
           <t>R$ 55,00</t>
         </is>
       </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+        <v>37</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
@@ -12715,7 +12711,7 @@
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12732,14 +12728,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12762,7 +12758,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12770,8 +12766,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="2" t="n">
-        <v>0</v>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -12780,39 +12778,41 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12835,33 +12835,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,7%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12878,14 +12878,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12919,9 +12919,9 @@
       <c r="I169" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12951,14 +12951,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12986,20 +12986,20 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,7%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13024,78 +13024,224 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-033</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza sem pé -1740</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>4536532951</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="n">
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
+++ b/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -889,10 +889,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -901,41 +899,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -967,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1001,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1078,14 +1074,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1111,17 +1107,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1151,12 +1147,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1228,14 +1224,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1258,33 +1254,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1301,14 +1297,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1331,7 +1327,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1339,8 +1335,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1349,39 +1347,41 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1409,20 +1409,20 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1447,14 +1447,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1480,17 +1480,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1520,14 +1520,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1559,24 +1559,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▲ 700,0%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1593,14 +1593,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1623,33 +1623,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1666,14 +1666,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1739,14 +1739,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1778,24 +1778,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1812,14 +1812,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1885,14 +1885,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1924,11 +1924,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1958,14 +1958,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -1999,9 +1999,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2104,14 +2104,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2143,11 +2143,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2250,14 +2250,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2289,11 +2289,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2323,14 +2323,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2356,17 +2356,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2396,14 +2396,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2435,11 +2435,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2469,14 +2469,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2499,33 +2499,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2542,14 +2542,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2615,14 +2615,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2654,24 +2654,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2688,14 +2688,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2729,9 +2729,9 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2761,14 +2761,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2800,11 +2800,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2834,14 +2834,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2873,11 +2873,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2907,14 +2907,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2980,14 +2980,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3019,11 +3019,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3126,14 +3126,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3165,11 +3165,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3272,14 +3272,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3345,12 +3345,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3418,14 +3418,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3459,9 +3459,9 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3491,14 +3491,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3532,9 +3532,9 @@
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3564,14 +3564,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3603,11 +3603,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3637,14 +3637,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3670,17 +3670,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3751,9 +3751,9 @@
       <c r="I45" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3783,14 +3783,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3813,33 +3813,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 77,8%</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3856,14 +3856,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3895,11 +3895,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3929,14 +3929,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3968,24 +3968,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4002,14 +4002,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4041,11 +4041,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4075,14 +4075,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4148,14 +4148,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4187,11 +4187,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4294,14 +4294,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4333,11 +4333,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4440,14 +4440,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4473,17 +4473,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4513,14 +4513,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4554,9 +4554,9 @@
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4586,14 +4586,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4616,33 +4616,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4659,14 +4659,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4692,17 +4692,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4732,14 +4732,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4771,24 +4771,24 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4805,14 +4805,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4835,33 +4835,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4878,14 +4878,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4911,17 +4911,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4951,14 +4951,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4989,10 +4989,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I62" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5001,41 +4999,39 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5058,33 +5054,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5101,12 +5097,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5178,14 +5174,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5208,7 +5204,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5217,24 +5213,24 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5251,12 +5247,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5328,14 +5324,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5367,11 +5363,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5401,12 +5397,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5478,14 +5474,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5517,11 +5513,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5551,12 +5547,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5628,14 +5624,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5667,11 +5663,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5701,14 +5697,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5731,7 +5727,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5739,8 +5735,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>0</v>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5749,39 +5747,41 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5813,11 +5813,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5847,14 +5847,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5880,17 +5880,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5920,14 +5920,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -5959,11 +5959,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5993,14 +5993,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6023,33 +6023,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6107,9 +6107,9 @@
       <c r="I77" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6139,14 +6139,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6174,20 +6174,20 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6212,14 +6212,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6251,11 +6251,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6285,14 +6285,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6324,24 +6324,24 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6358,14 +6358,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6397,11 +6397,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6431,14 +6431,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6470,11 +6470,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6504,14 +6504,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6543,11 +6543,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6577,14 +6577,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6616,11 +6616,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6650,14 +6650,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6689,11 +6689,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6723,14 +6723,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6762,11 +6762,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6869,14 +6869,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -6908,11 +6908,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6983,9 +6983,9 @@
       <c r="I89" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7015,14 +7015,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7054,11 +7054,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7088,14 +7088,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7127,11 +7127,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7161,14 +7161,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7200,11 +7200,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7234,14 +7234,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7272,10 +7272,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7284,41 +7282,39 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7350,11 +7346,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7384,12 +7380,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7461,14 +7457,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7500,11 +7496,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7534,14 +7530,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7564,7 +7560,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7572,8 +7568,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7582,39 +7580,41 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7646,11 +7646,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7680,12 +7680,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7753,14 +7753,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7792,11 +7792,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7826,14 +7826,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7864,10 +7864,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -7876,39 +7874,37 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7976,12 +7972,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8053,12 +8049,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8094,9 +8090,9 @@
       <c r="I104" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8126,14 +8122,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8156,7 +8152,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8164,8 +8160,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="2" t="n">
-        <v>0</v>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8174,39 +8172,41 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8238,11 +8238,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8272,14 +8272,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8313,9 +8313,9 @@
       <c r="I107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8345,14 +8345,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8384,11 +8384,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8418,14 +8418,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8457,11 +8457,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8491,14 +8491,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8530,11 +8530,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8564,14 +8564,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8602,10 +8602,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I111" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8614,41 +8612,39 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8680,11 +8676,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8714,12 +8710,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8791,14 +8787,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8830,11 +8826,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8864,12 +8860,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8941,14 +8937,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -8980,11 +8976,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9007,21 +9003,21 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9044,7 +9040,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9052,8 +9048,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="2" t="n">
-        <v>0</v>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
@@ -9062,39 +9060,41 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9126,11 +9126,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9160,14 +9160,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9201,9 +9201,9 @@
       <c r="I119" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9306,14 +9306,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9345,11 +9345,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9420,9 +9420,9 @@
       <c r="I122" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9452,14 +9452,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9485,17 +9485,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H123" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9525,14 +9525,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9564,11 +9564,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9598,14 +9598,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9628,33 +9628,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9671,14 +9671,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9704,17 +9704,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9744,14 +9744,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9782,10 +9782,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I127" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9794,41 +9792,39 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -9851,33 +9847,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9894,12 +9890,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9971,14 +9967,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10001,7 +9997,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -10010,24 +10006,24 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10044,12 +10040,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10121,14 +10117,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10160,11 +10156,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>▲ 1100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10194,12 +10190,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10271,14 +10267,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10310,11 +10306,11 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1100,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10344,12 +10340,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10421,14 +10417,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10454,17 +10450,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10494,12 +10490,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10571,14 +10567,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10601,33 +10597,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10644,12 +10640,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10721,14 +10717,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10751,33 +10747,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10794,12 +10790,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10871,14 +10867,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -10901,33 +10897,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▼ 90,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -10944,12 +10940,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11021,14 +11017,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11056,20 +11052,20 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>▲ 34,2%</t>
+          <t>▼ 90,2%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
@@ -11077,7 +11073,7 @@
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11094,12 +11090,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11171,14 +11167,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11201,33 +11197,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>51</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 34,2%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11244,12 +11240,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11321,14 +11317,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11351,33 +11347,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11394,12 +11390,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11471,14 +11467,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11504,22 +11500,22 @@
           <t>R$ 142,00</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>38</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
@@ -11527,7 +11523,7 @@
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11544,12 +11540,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11621,14 +11617,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11651,33 +11647,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 71,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 142,00</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11694,14 +11690,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11724,7 +11720,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -11732,8 +11728,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" s="2" t="n">
-        <v>0</v>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -11742,39 +11740,41 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11797,33 +11797,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 71,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>▲ 7,9%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11840,14 +11840,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11881,9 +11881,9 @@
       <c r="I155" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -11913,14 +11913,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -11943,33 +11943,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▲ 18,8%</t>
+        <v>41</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11986,14 +11986,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12025,11 +12025,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12059,14 +12059,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12092,22 +12092,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>▼ 62,8%</t>
+          <t>▲ 18,8%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12132,12 +12132,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12205,14 +12205,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12235,33 +12235,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>▲ 24,9%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▼ 62,8%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12278,14 +12278,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12316,10 +12316,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I161" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -12328,41 +12326,39 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12385,25 +12381,25 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
+          <t>R$ 276,00</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,2%</t>
+          <t>▲ 24,9%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,0%</t>
+        <v>86</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
@@ -12411,7 +12407,7 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12428,12 +12424,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12505,14 +12501,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12535,33 +12531,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 331,00</t>
+          <t>R$ 221,00</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>▲ 501,8%</t>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▲ 97,3%</t>
+        <v>81</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12578,12 +12574,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12655,14 +12651,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12685,33 +12681,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 331,00</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 501,8%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▼ 2,6%</t>
+          <t>▲ 97,3%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12728,12 +12724,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12805,14 +12801,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12838,22 +12834,22 @@
           <t>R$ 55,00</t>
         </is>
       </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,6%</t>
+        <v>37</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
@@ -12861,7 +12857,7 @@
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12878,14 +12874,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12908,7 +12904,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -12916,8 +12912,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I169" s="2" t="n">
-        <v>0</v>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
@@ -12926,39 +12924,41 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -12981,33 +12981,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,7%</t>
+          <t>▼ 15,6%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13024,14 +13024,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -13065,9 +13065,9 @@
       <c r="I171" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J171" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13097,14 +13097,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-033</t>
@@ -13132,20 +13132,20 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>45</v>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,7%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13170,78 +13170,224 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-033</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza sem pé -1740</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>4536532951</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="n">
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
+++ b/saida_skus/SKU_UTD-033-BOLEIRA-VITTAZA-SEM-PE-1740.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -819,9 +819,9 @@
       <c r="I5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1035,51 +1035,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1113,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1147,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1177,59 +1173,55 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1257,17 +1249,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1297,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1327,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1335,51 +1327,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1404,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1447,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1486,7 +1474,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1520,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1550,7 +1538,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1559,24 +1547,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1593,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1623,55 +1611,59 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1705,11 +1697,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▲ 700,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1739,12 +1731,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1769,7 +1761,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1777,47 +1769,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1845,17 +1841,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1885,12 +1881,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1915,7 +1911,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1923,47 +1919,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1988,33 +1988,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2070,11 +2070,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2143,24 +2143,24 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2210,17 +2210,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2289,11 +2289,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 700,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2362,24 +2362,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2435,11 +2435,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2542,12 +2542,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2615,12 +2615,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2654,24 +2654,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2688,12 +2688,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2729,9 +2729,9 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2761,12 +2761,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2800,11 +2800,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2873,11 +2873,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2980,12 +2980,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3019,11 +3019,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3086,17 +3086,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3165,11 +3165,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3238,24 +3238,24 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3345,12 +3345,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3384,11 +3384,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3459,9 +3459,9 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3564,12 +3564,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3603,11 +3603,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3678,9 +3678,9 @@
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3749,11 +3749,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3783,12 +3783,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3816,17 +3816,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3895,11 +3895,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3968,24 +3968,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 77,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4041,11 +4041,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4148,12 +4148,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4187,11 +4187,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4262,9 +4262,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4335,9 +4335,9 @@
       <c r="I53" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4400,17 +4400,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4479,11 +4479,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4552,24 +4552,24 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4586,12 +4586,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4619,17 +4619,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4698,11 +4698,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4771,24 +4771,24 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4805,12 +4805,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4838,17 +4838,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4917,11 +4917,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -4999,15 +4999,15 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5057,17 +5057,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5135,10 +5135,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5147,39 +5145,37 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5204,33 +5200,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5247,12 +5243,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5277,7 +5273,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5285,51 +5281,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5354,7 +5346,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5363,24 +5355,24 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5397,12 +5389,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5427,59 +5419,55 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5513,11 +5501,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5547,12 +5535,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5577,7 +5565,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5585,10 +5573,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5597,39 +5583,37 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5657,17 +5641,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5697,12 +5681,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5774,12 +5758,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5804,7 +5788,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5817,20 +5801,20 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5847,12 +5831,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5877,7 +5861,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5885,8 +5869,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>0</v>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5895,37 +5881,39 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5959,11 +5947,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5993,12 +5981,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6023,55 +6011,59 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6107,9 +6099,9 @@
       <c r="I77" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6139,12 +6131,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6169,55 +6161,59 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6251,11 +6247,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6285,12 +6281,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6315,7 +6311,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6323,47 +6319,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6397,11 +6397,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6470,11 +6470,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6545,9 +6545,9 @@
       <c r="I83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6610,17 +6610,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6650,12 +6650,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6689,11 +6689,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6753,33 +6753,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6837,9 +6837,9 @@
       <c r="I87" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6908,24 +6908,24 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6981,11 +6981,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7088,12 +7088,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7127,11 +7127,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7200,11 +7200,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7273,11 +7273,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7346,11 +7346,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7418,51 +7418,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7496,11 +7492,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7530,12 +7526,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7560,7 +7556,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7568,51 +7564,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7646,11 +7638,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7680,12 +7672,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7719,11 +7711,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7753,12 +7745,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7792,11 +7784,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7826,12 +7818,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7865,7 +7857,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -7899,12 +7891,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7938,11 +7930,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7972,12 +7964,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8049,12 +8041,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8090,9 +8082,9 @@
       <c r="I104" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8122,12 +8114,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8199,12 +8191,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8238,11 +8230,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8272,12 +8264,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8345,12 +8337,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8384,11 +8376,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8418,12 +8410,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8459,9 +8451,9 @@
       <c r="I109" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8491,12 +8483,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8530,11 +8522,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8564,12 +8556,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8594,7 +8586,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8602,8 +8594,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>1</v>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8612,37 +8606,39 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8676,11 +8672,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8710,12 +8706,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8787,12 +8783,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8826,11 +8822,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8860,12 +8856,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8890,7 +8886,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -8898,10 +8894,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -8910,39 +8904,37 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8976,11 +8968,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9010,12 +9002,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9040,7 +9032,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9048,51 +9040,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9126,11 +9114,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9153,19 +9141,19 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9199,7 +9187,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
@@ -9226,19 +9214,19 @@
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9272,11 +9260,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9299,19 +9287,19 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9336,7 +9324,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9344,47 +9332,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9418,11 +9410,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9445,19 +9437,19 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9482,7 +9474,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9490,8 +9482,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="n">
-        <v>1</v>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9500,37 +9494,39 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9564,11 +9560,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9591,19 +9587,19 @@
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9628,55 +9624,59 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9712,9 +9712,9 @@
       <c r="I126" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9792,15 +9792,15 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9817,12 +9817,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9850,17 +9850,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9890,12 +9890,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -9928,51 +9928,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -9997,7 +9993,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -10006,24 +10002,24 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J130" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>3</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10040,12 +10036,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10070,7 +10066,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10078,10 +10074,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I131" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -10090,39 +10084,37 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10156,11 +10148,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10190,12 +10182,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10220,59 +10212,55 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10306,11 +10294,11 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10340,12 +10328,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10370,7 +10358,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10378,10 +10366,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10390,39 +10376,37 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10450,17 +10434,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10490,12 +10474,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10567,12 +10551,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10597,33 +10581,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10640,12 +10624,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10717,12 +10701,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10747,7 +10731,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -10756,24 +10740,24 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10790,12 +10774,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10867,12 +10851,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -10900,17 +10884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 1100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10940,12 +10924,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11017,12 +11001,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11047,33 +11031,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I144" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,2%</t>
-        </is>
-      </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11090,12 +11074,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11167,12 +11151,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11197,33 +11181,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,00</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>▲ 34,2%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11240,12 +11224,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11317,12 +11301,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11347,33 +11331,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11390,12 +11374,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11467,12 +11451,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11497,33 +11481,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>▲ 46,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11540,12 +11524,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11617,12 +11601,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11647,33 +11631,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 142,00</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 69,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 90,2%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11690,12 +11674,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11767,12 +11751,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11797,7 +11781,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 71,00</t>
+          <t>R$ 69,00</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -11806,16 +11790,16 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,5%</t>
+          <t>▲ 34,2%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
@@ -11823,7 +11807,7 @@
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11840,12 +11824,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11870,7 +11854,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -11878,8 +11862,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="2" t="n">
-        <v>0</v>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -11888,37 +11874,39 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -11946,17 +11934,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
+      <c r="H156" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,9%</t>
+        <v>38</v>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11986,12 +11974,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12016,7 +12004,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12024,47 +12012,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12089,7 +12081,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 142,00</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -12100,22 +12092,22 @@
       <c r="I158" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,8%</t>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12132,12 +12124,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12162,7 +12154,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12170,47 +12162,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="n">
-        <v>1</v>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12235,33 +12231,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 142,00</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,8%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12278,12 +12274,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12308,7 +12304,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12316,8 +12312,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="2" t="n">
-        <v>1</v>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -12326,37 +12324,39 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12381,33 +12381,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 24,9%</t>
+          <t>R$ 71,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>▲ 6,2%</t>
+          <t>▼ 41,5%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12462,10 +12462,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I163" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -12474,39 +12472,37 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12531,33 +12527,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,0%</t>
+        <v>41</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,9%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12574,12 +12570,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12604,7 +12600,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12612,51 +12608,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12681,33 +12673,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 331,00</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 501,8%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 97,3%</t>
+        <v>38</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,8%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12724,12 +12716,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12754,7 +12746,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12762,51 +12754,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I167" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12831,25 +12819,25 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 2,6%</t>
+        <v>32</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▼ 62,8%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
@@ -12857,7 +12845,7 @@
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12874,12 +12862,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -12904,7 +12892,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -12912,10 +12900,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I169" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
@@ -12924,39 +12910,37 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -12981,33 +12965,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 276,00</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▲ 24,9%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,6%</t>
+          <t>▲ 6,2%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13024,12 +13008,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13054,7 +13038,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -13062,8 +13046,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I171" s="2" t="n">
-        <v>0</v>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
@@ -13072,37 +13058,39 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13127,33 +13115,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 221,00</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,2%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J172" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,7%</t>
+        <v>81</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13170,12 +13158,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13200,7 +13188,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -13208,47 +13196,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J173" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13273,33 +13265,33 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>R$ 166,00</t>
-        </is>
-      </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 331,00</t>
+        </is>
+      </c>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>▲ 501,8%</t>
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>73</v>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>▲ 97,3%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="L174" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -13316,78 +13308,670 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>▼ 2,6%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,6%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,7%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4536532951</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-033</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza sem pé -1740</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>6470954398</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 166,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-033</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza sem pé -1740</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4536532951</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="n">
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>